--- a/和美智慧校園/和美智慧校園_員工主檔整理版_2026-07-10.xlsx
+++ b/和美智慧校園/和美智慧校園_員工主檔整理版_2026-07-10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\自動備份資料夾\Documents\GitHub\Heremay-Smart-Campus\和美智慧校園 v8｜巡堂雙週直式滿版 PDF 完成版\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\自動備份資料夾\Documents\GitHub\Heremay-Smart-Campus\和美智慧校園\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2DE482-4725-402E-8918-EA91DB29DAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB038E3-30A4-47E9-B778-5F4FF9C6868A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="首頁摘要" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="337">
   <si>
     <t>和美智慧校園｜員工主檔整理版</t>
   </si>
@@ -1043,6 +1043,10 @@
   </si>
   <si>
     <t>人資備註2</t>
+  </si>
+  <si>
+    <t>女</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1052,7 +1056,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1082,6 +1086,12 @@
       <sz val="9"/>
       <name val="細明體"/>
       <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -1136,7 +1146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1175,6 +1185,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5339,7 +5352,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="57">
+    <row r="8" spans="1:57" ht="57.75">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -5355,7 +5368,9 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="H8" s="15" t="s">
+        <v>336</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -5392,7 +5407,9 @@
         <v>47</v>
       </c>
       <c r="AH8" s="5"/>
-      <c r="AI8" s="5"/>
+      <c r="AI8" s="5" t="s">
+        <v>253</v>
+      </c>
       <c r="AJ8" s="5"/>
       <c r="AK8" s="5"/>
       <c r="AL8" s="5" t="s">
